--- a/activity/M01A04/M01A04.xlsx
+++ b/activity/M01A04/M01A04.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\R.HCMC\activity\M01A04\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A5EA602A-1ED5-43C6-95EC-C1E0A595EE4A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7456F913-89E9-4C73-B8C1-835941927E19}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="15675" activeTab="1" xr2:uid="{CB4A84EB-58A9-4828-A1EC-5E14AACD60D5}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="15675" xr2:uid="{CB4A84EB-58A9-4828-A1EC-5E14AACD60D5}"/>
   </bookViews>
   <sheets>
     <sheet name="Calificacion" sheetId="12" r:id="rId1"/>
@@ -230,7 +230,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="14">
+  <borders count="17">
     <border>
       <left/>
       <right/>
@@ -356,19 +356,6 @@
     </border>
     <border>
       <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right/>
-      <top style="thin">
-        <color theme="0" tint="-4.9989318521683403E-2"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
         <color theme="0" tint="-4.9989318521683403E-2"/>
       </left>
       <right style="thin">
@@ -421,6 +408,58 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color theme="0" tint="-4.9989318521683403E-2"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color theme="0" tint="-4.9989318521683403E-2"/>
+      </right>
+      <top style="thin">
+        <color theme="0" tint="-4.9989318521683403E-2"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color theme="0" tint="-4.9989318521683403E-2"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color theme="0" tint="-4.9989318521683403E-2"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
@@ -430,7 +469,7 @@
     <xf numFmtId="43" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="39">
+  <cellXfs count="42">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
@@ -463,9 +502,6 @@
       <alignment horizontal="left" vertical="top" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="2" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
@@ -487,56 +523,32 @@
     <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="2" fontId="5" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="2" fontId="5" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="2" fontId="5" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="2" fontId="5" fillId="2" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    <xf numFmtId="2" fontId="10" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="2" fontId="10" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="2" fontId="10" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="13" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="2" fontId="10" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
@@ -547,6 +559,44 @@
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="12" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="2" fontId="10" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="2" fontId="10" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="2" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="5" fillId="2" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="6">
@@ -1947,315 +1997,313 @@
   <dimension ref="B1:F21"/>
   <sheetFormatPr defaultColWidth="11.33203125" defaultRowHeight="15.4" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="2.6640625" style="12" customWidth="1"/>
-    <col min="2" max="2" width="13.33203125" style="12" customWidth="1"/>
-    <col min="3" max="4" width="10.53125" style="12" customWidth="1"/>
-    <col min="5" max="5" width="13.53125" style="12" customWidth="1"/>
-    <col min="6" max="6" width="10.53125" style="12" customWidth="1"/>
-    <col min="7" max="7" width="2.6640625" style="12" customWidth="1"/>
-    <col min="8" max="16384" width="11.33203125" style="12"/>
+    <col min="1" max="1" width="2.6640625" style="11" customWidth="1"/>
+    <col min="2" max="2" width="13.33203125" style="11" customWidth="1"/>
+    <col min="3" max="4" width="10.53125" style="11" customWidth="1"/>
+    <col min="5" max="5" width="13.53125" style="11" customWidth="1"/>
+    <col min="6" max="6" width="10.53125" style="11" customWidth="1"/>
+    <col min="7" max="7" width="2.6640625" style="11" customWidth="1"/>
+    <col min="8" max="16384" width="11.33203125" style="11"/>
   </cols>
   <sheetData>
     <row r="1" spans="2:6" x14ac:dyDescent="0.45">
-      <c r="F1" s="38" t="s">
+      <c r="F1" s="29" t="s">
         <v>26</v>
       </c>
     </row>
     <row r="2" spans="2:6" x14ac:dyDescent="0.45">
-      <c r="B2" s="23" t="s">
+      <c r="B2" s="30" t="s">
         <v>22</v>
       </c>
-      <c r="C2" s="23"/>
-      <c r="D2" s="23"/>
-      <c r="E2" s="23"/>
-      <c r="F2" s="23"/>
+      <c r="C2" s="30"/>
+      <c r="D2" s="30"/>
+      <c r="E2" s="30"/>
+      <c r="F2" s="30"/>
     </row>
     <row r="3" spans="2:6" x14ac:dyDescent="0.45">
-      <c r="B3" s="23"/>
-      <c r="C3" s="23"/>
-      <c r="D3" s="23"/>
-      <c r="E3" s="23"/>
-      <c r="F3" s="23"/>
+      <c r="B3" s="30"/>
+      <c r="C3" s="30"/>
+      <c r="D3" s="30"/>
+      <c r="E3" s="30"/>
+      <c r="F3" s="30"/>
     </row>
     <row r="4" spans="2:6" ht="33.75" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="B4" s="18" t="s">
+      <c r="B4" s="17" t="s">
         <v>2</v>
       </c>
-      <c r="C4" s="19" t="s">
+      <c r="C4" s="18" t="s">
         <v>11</v>
       </c>
-      <c r="D4" s="19" t="s">
+      <c r="D4" s="18" t="s">
         <v>5</v>
       </c>
-      <c r="E4" s="19" t="s">
+      <c r="E4" s="18" t="s">
         <v>12</v>
       </c>
-      <c r="F4" s="20" t="s">
+      <c r="F4" s="19" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="5" spans="2:6" x14ac:dyDescent="0.45">
-      <c r="B5" s="13" t="s">
+      <c r="B5" s="12" t="s">
         <v>6</v>
       </c>
-      <c r="C5" s="30">
+      <c r="C5" s="22">
         <v>5</v>
       </c>
-      <c r="D5" s="21">
+      <c r="D5" s="20">
         <f>Detalle!C10*C5/5</f>
         <v>0</v>
       </c>
-      <c r="E5" s="32">
+      <c r="E5" s="24"/>
+      <c r="F5" s="13">
+        <f>AVERAGE(D5:E5)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="2:6" x14ac:dyDescent="0.45">
+      <c r="B6" s="12" t="s">
+        <v>7</v>
+      </c>
+      <c r="C6" s="22">
         <v>5</v>
       </c>
-      <c r="F5" s="14">
-        <f>AVERAGE(D5:E5)</f>
-        <v>2.5</v>
-      </c>
-    </row>
-    <row r="6" spans="2:6" x14ac:dyDescent="0.45">
-      <c r="B6" s="13" t="s">
-        <v>7</v>
-      </c>
-      <c r="C6" s="30">
+      <c r="D6" s="20">
+        <f>Detalle!E10*C6/5</f>
+        <v>0</v>
+      </c>
+      <c r="E6" s="24"/>
+      <c r="F6" s="13">
+        <f t="shared" ref="F6:F18" si="0">AVERAGE(D6:E6)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="2:6" x14ac:dyDescent="0.45">
+      <c r="B7" s="12" t="s">
+        <v>8</v>
+      </c>
+      <c r="C7" s="22">
         <v>5</v>
       </c>
-      <c r="D6" s="21">
-        <f>Detalle!E10*C6/5</f>
-        <v>0</v>
-      </c>
-      <c r="E6" s="32"/>
-      <c r="F6" s="14">
-        <f t="shared" ref="F6:F18" si="0">AVERAGE(D6:E6)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" spans="2:6" x14ac:dyDescent="0.45">
-      <c r="B7" s="13" t="s">
-        <v>8</v>
-      </c>
-      <c r="C7" s="30">
+      <c r="D7" s="20">
+        <f>Detalle!G10*C7/5</f>
+        <v>0</v>
+      </c>
+      <c r="E7" s="24"/>
+      <c r="F7" s="13">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="2:6" x14ac:dyDescent="0.45">
+      <c r="B8" s="12" t="s">
+        <v>9</v>
+      </c>
+      <c r="C8" s="22">
         <v>5</v>
       </c>
-      <c r="D7" s="21">
-        <f>Detalle!G10*C7/5</f>
-        <v>0</v>
-      </c>
-      <c r="E7" s="32"/>
-      <c r="F7" s="14">
+      <c r="D8" s="20">
+        <f>Detalle!I10*C8/5</f>
+        <v>0</v>
+      </c>
+      <c r="E8" s="24"/>
+      <c r="F8" s="13">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="2:6" x14ac:dyDescent="0.45">
-      <c r="B8" s="13" t="s">
-        <v>9</v>
-      </c>
-      <c r="C8" s="30">
+    <row r="9" spans="2:6" x14ac:dyDescent="0.45">
+      <c r="B9" s="12" t="s">
+        <v>10</v>
+      </c>
+      <c r="C9" s="22">
         <v>5</v>
       </c>
-      <c r="D8" s="21">
-        <f>Detalle!I10*C8/5</f>
-        <v>0</v>
-      </c>
-      <c r="E8" s="32"/>
-      <c r="F8" s="14">
+      <c r="D9" s="20">
+        <f>Detalle!K10*C9/5</f>
+        <v>0</v>
+      </c>
+      <c r="E9" s="24"/>
+      <c r="F9" s="13">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="2:6" x14ac:dyDescent="0.45">
-      <c r="B9" s="13" t="s">
-        <v>10</v>
-      </c>
-      <c r="C9" s="30">
+    <row r="10" spans="2:6" x14ac:dyDescent="0.45">
+      <c r="B10" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="C10" s="22">
         <v>5</v>
       </c>
-      <c r="D9" s="21">
-        <f>Detalle!K10*C9/5</f>
-        <v>0</v>
-      </c>
-      <c r="E9" s="32"/>
-      <c r="F9" s="14">
+      <c r="D10" s="20">
+        <f>Detalle!M10*C10/5</f>
+        <v>0</v>
+      </c>
+      <c r="E10" s="24"/>
+      <c r="F10" s="13">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="2:6" x14ac:dyDescent="0.45">
-      <c r="B10" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="C10" s="30">
+    <row r="11" spans="2:6" x14ac:dyDescent="0.45">
+      <c r="B11" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="C11" s="22">
         <v>5</v>
       </c>
-      <c r="D10" s="21">
-        <f>Detalle!M10*C10/5</f>
-        <v>0</v>
-      </c>
-      <c r="E10" s="32"/>
-      <c r="F10" s="14">
+      <c r="D11" s="20">
+        <f>Detalle!O10*C11/5</f>
+        <v>0</v>
+      </c>
+      <c r="E11" s="24"/>
+      <c r="F11" s="13">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="2:6" x14ac:dyDescent="0.45">
-      <c r="B11" s="13" t="s">
-        <v>14</v>
-      </c>
-      <c r="C11" s="30">
+    <row r="12" spans="2:6" x14ac:dyDescent="0.45">
+      <c r="B12" s="12" t="s">
+        <v>15</v>
+      </c>
+      <c r="C12" s="22">
         <v>5</v>
       </c>
-      <c r="D11" s="21">
-        <f>Detalle!O10*C11/5</f>
-        <v>0</v>
-      </c>
-      <c r="E11" s="32"/>
-      <c r="F11" s="14">
+      <c r="D12" s="20">
+        <f>Detalle!Q10*C12/5</f>
+        <v>0</v>
+      </c>
+      <c r="E12" s="24"/>
+      <c r="F12" s="13">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="2:6" x14ac:dyDescent="0.45">
-      <c r="B12" s="13" t="s">
-        <v>15</v>
-      </c>
-      <c r="C12" s="30">
+    <row r="13" spans="2:6" x14ac:dyDescent="0.45">
+      <c r="B13" s="12" t="s">
+        <v>16</v>
+      </c>
+      <c r="C13" s="22">
         <v>5</v>
       </c>
-      <c r="D12" s="21">
-        <f>Detalle!Q10*C12/5</f>
-        <v>0</v>
-      </c>
-      <c r="E12" s="32"/>
-      <c r="F12" s="14">
+      <c r="D13" s="20">
+        <f>Detalle!S10*C13/5</f>
+        <v>0</v>
+      </c>
+      <c r="E13" s="24"/>
+      <c r="F13" s="13">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="2:6" x14ac:dyDescent="0.45">
-      <c r="B13" s="13" t="s">
-        <v>16</v>
-      </c>
-      <c r="C13" s="30">
+    <row r="14" spans="2:6" x14ac:dyDescent="0.45">
+      <c r="B14" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="C14" s="22">
         <v>5</v>
       </c>
-      <c r="D13" s="21">
-        <f>Detalle!S10*C13/5</f>
-        <v>0</v>
-      </c>
-      <c r="E13" s="32"/>
-      <c r="F13" s="14">
+      <c r="D14" s="20">
+        <f>Detalle!U10*C14/5</f>
+        <v>0</v>
+      </c>
+      <c r="E14" s="24"/>
+      <c r="F14" s="13">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="2:6" x14ac:dyDescent="0.45">
-      <c r="B14" s="13" t="s">
-        <v>17</v>
-      </c>
-      <c r="C14" s="30">
+    <row r="15" spans="2:6" x14ac:dyDescent="0.45">
+      <c r="B15" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="C15" s="22">
         <v>5</v>
       </c>
-      <c r="D14" s="21">
-        <f>Detalle!U10*C14/5</f>
-        <v>0</v>
-      </c>
-      <c r="E14" s="32"/>
-      <c r="F14" s="14">
+      <c r="D15" s="20">
+        <f>Detalle!W10*C15/5</f>
+        <v>0</v>
+      </c>
+      <c r="E15" s="24"/>
+      <c r="F15" s="13">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="2:6" x14ac:dyDescent="0.45">
-      <c r="B15" s="13" t="s">
-        <v>18</v>
-      </c>
-      <c r="C15" s="30">
+    <row r="16" spans="2:6" x14ac:dyDescent="0.45">
+      <c r="B16" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="C16" s="22">
         <v>5</v>
       </c>
-      <c r="D15" s="21">
-        <f>Detalle!W10*C15/5</f>
-        <v>0</v>
-      </c>
-      <c r="E15" s="32"/>
-      <c r="F15" s="14">
+      <c r="D16" s="20">
+        <f>Detalle!Y10*C16/5</f>
+        <v>0</v>
+      </c>
+      <c r="E16" s="24"/>
+      <c r="F16" s="13">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="2:6" x14ac:dyDescent="0.45">
-      <c r="B16" s="13" t="s">
-        <v>19</v>
-      </c>
-      <c r="C16" s="30">
+    <row r="17" spans="2:6" x14ac:dyDescent="0.45">
+      <c r="B17" s="12" t="s">
+        <v>20</v>
+      </c>
+      <c r="C17" s="22">
         <v>5</v>
       </c>
-      <c r="D16" s="21">
-        <f>Detalle!Y10*C16/5</f>
-        <v>0</v>
-      </c>
-      <c r="E16" s="32"/>
-      <c r="F16" s="14">
+      <c r="D17" s="20">
+        <f>Detalle!AA10*C17/5</f>
+        <v>0</v>
+      </c>
+      <c r="E17" s="24"/>
+      <c r="F17" s="13">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="2:6" x14ac:dyDescent="0.45">
-      <c r="B17" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="C17" s="30">
+    <row r="18" spans="2:6" x14ac:dyDescent="0.45">
+      <c r="B18" s="14" t="s">
+        <v>21</v>
+      </c>
+      <c r="C18" s="23">
         <v>5</v>
       </c>
-      <c r="D17" s="21">
-        <f>Detalle!AA10*C17/5</f>
-        <v>0</v>
-      </c>
-      <c r="E17" s="32"/>
-      <c r="F17" s="14">
+      <c r="D18" s="21">
+        <f>Detalle!AC10*C18/5</f>
+        <v>0</v>
+      </c>
+      <c r="E18" s="25"/>
+      <c r="F18" s="15">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="2:6" x14ac:dyDescent="0.45">
-      <c r="B18" s="15" t="s">
-        <v>21</v>
-      </c>
-      <c r="C18" s="31">
-        <v>5</v>
-      </c>
-      <c r="D18" s="22">
-        <f>Detalle!AC10*C18/5</f>
-        <v>0</v>
-      </c>
-      <c r="E18" s="33"/>
-      <c r="F18" s="16">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
     <row r="19" spans="2:6" ht="15.4" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="B19" s="35" t="s">
+      <c r="B19" s="31" t="s">
         <v>23</v>
       </c>
-      <c r="C19" s="35"/>
-      <c r="D19" s="35"/>
-      <c r="E19" s="35"/>
-      <c r="F19" s="35"/>
+      <c r="C19" s="31"/>
+      <c r="D19" s="31"/>
+      <c r="E19" s="31"/>
+      <c r="F19" s="31"/>
     </row>
     <row r="20" spans="2:6" x14ac:dyDescent="0.45">
-      <c r="B20" s="34"/>
-      <c r="C20" s="34"/>
-      <c r="D20" s="34"/>
-      <c r="E20" s="34"/>
-      <c r="F20" s="34"/>
+      <c r="B20" s="26"/>
+      <c r="C20" s="26"/>
+      <c r="D20" s="26"/>
+      <c r="E20" s="26"/>
+      <c r="F20" s="26"/>
     </row>
     <row r="21" spans="2:6" x14ac:dyDescent="0.45">
-      <c r="B21" s="34"/>
-      <c r="C21" s="34"/>
-      <c r="D21" s="34"/>
-      <c r="E21" s="34"/>
-      <c r="F21" s="34"/>
+      <c r="B21" s="26"/>
+      <c r="C21" s="26"/>
+      <c r="D21" s="26"/>
+      <c r="E21" s="26"/>
+      <c r="F21" s="26"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -2320,82 +2368,82 @@
     </row>
     <row r="2" spans="1:30" s="4" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A2" s="7"/>
-      <c r="B2" s="24" t="s">
+      <c r="B2" s="32" t="s">
         <v>3</v>
       </c>
-      <c r="C2" s="28" t="str">
+      <c r="C2" s="34" t="str">
         <f>Calificacion!$B5</f>
         <v>Grupo 1</v>
       </c>
-      <c r="D2" s="29"/>
-      <c r="E2" s="28" t="str">
+      <c r="D2" s="35"/>
+      <c r="E2" s="34" t="str">
         <f>Calificacion!$B6</f>
         <v>Grupo 2</v>
       </c>
-      <c r="F2" s="29"/>
-      <c r="G2" s="28" t="str">
+      <c r="F2" s="35"/>
+      <c r="G2" s="34" t="str">
         <f>Calificacion!$B7</f>
         <v>Grupo 3</v>
       </c>
-      <c r="H2" s="29"/>
-      <c r="I2" s="28" t="str">
+      <c r="H2" s="35"/>
+      <c r="I2" s="34" t="str">
         <f>Calificacion!$B8</f>
         <v>Grupo 4</v>
       </c>
-      <c r="J2" s="29"/>
-      <c r="K2" s="28" t="str">
+      <c r="J2" s="35"/>
+      <c r="K2" s="34" t="str">
         <f>Calificacion!$B9</f>
         <v>Grupo 5</v>
       </c>
-      <c r="L2" s="29"/>
-      <c r="M2" s="28" t="str">
+      <c r="L2" s="35"/>
+      <c r="M2" s="34" t="str">
         <f>Calificacion!$B10</f>
         <v>Grupo 6</v>
       </c>
-      <c r="N2" s="29"/>
-      <c r="O2" s="28" t="str">
+      <c r="N2" s="35"/>
+      <c r="O2" s="34" t="str">
         <f>Calificacion!$B11</f>
         <v>Grupo 7</v>
       </c>
-      <c r="P2" s="29"/>
-      <c r="Q2" s="28" t="str">
+      <c r="P2" s="35"/>
+      <c r="Q2" s="34" t="str">
         <f>Calificacion!$B12</f>
         <v>Grupo 8</v>
       </c>
-      <c r="R2" s="29"/>
-      <c r="S2" s="28" t="str">
+      <c r="R2" s="35"/>
+      <c r="S2" s="34" t="str">
         <f>Calificacion!$B13</f>
         <v>Grupo 9</v>
       </c>
-      <c r="T2" s="29"/>
-      <c r="U2" s="28" t="str">
+      <c r="T2" s="35"/>
+      <c r="U2" s="34" t="str">
         <f>Calificacion!$B14</f>
         <v>Grupo 10</v>
       </c>
-      <c r="V2" s="29"/>
-      <c r="W2" s="28" t="str">
+      <c r="V2" s="35"/>
+      <c r="W2" s="34" t="str">
         <f>Calificacion!$B15</f>
         <v>Grupo 11</v>
       </c>
-      <c r="X2" s="29"/>
-      <c r="Y2" s="28" t="str">
+      <c r="X2" s="35"/>
+      <c r="Y2" s="34" t="str">
         <f>Calificacion!$B16</f>
         <v>Grupo 12</v>
       </c>
-      <c r="Z2" s="29"/>
-      <c r="AA2" s="28" t="str">
+      <c r="Z2" s="35"/>
+      <c r="AA2" s="34" t="str">
         <f>Calificacion!$B17</f>
         <v>Grupo 13</v>
       </c>
-      <c r="AB2" s="29"/>
-      <c r="AC2" s="28" t="str">
+      <c r="AB2" s="35"/>
+      <c r="AC2" s="34" t="str">
         <f>Calificacion!$B18</f>
         <v>Grupo 14</v>
       </c>
-      <c r="AD2" s="29"/>
+      <c r="AD2" s="35"/>
     </row>
     <row r="3" spans="1:30" x14ac:dyDescent="0.45">
-      <c r="B3" s="25"/>
+      <c r="B3" s="33"/>
       <c r="C3" s="8" t="s">
         <v>1</v>
       </c>
@@ -2485,304 +2533,304 @@
       <c r="B4" s="10" t="s">
         <v>24</v>
       </c>
-      <c r="C4" s="36">
-        <v>0</v>
-      </c>
-      <c r="D4" s="37"/>
-      <c r="E4" s="36">
-        <v>0</v>
-      </c>
-      <c r="F4" s="37"/>
-      <c r="G4" s="36">
-        <v>0</v>
-      </c>
-      <c r="H4" s="37"/>
-      <c r="I4" s="36">
-        <v>0</v>
-      </c>
-      <c r="J4" s="37"/>
-      <c r="K4" s="36">
-        <v>0</v>
-      </c>
-      <c r="L4" s="37"/>
-      <c r="M4" s="36">
-        <v>0</v>
-      </c>
-      <c r="N4" s="37"/>
-      <c r="O4" s="36">
-        <v>0</v>
-      </c>
-      <c r="P4" s="37"/>
-      <c r="Q4" s="36">
-        <v>0</v>
-      </c>
-      <c r="R4" s="37"/>
-      <c r="S4" s="36">
-        <v>0</v>
-      </c>
-      <c r="T4" s="37"/>
-      <c r="U4" s="36">
-        <v>0</v>
-      </c>
-      <c r="V4" s="37"/>
-      <c r="W4" s="36">
-        <v>0</v>
-      </c>
-      <c r="X4" s="37"/>
-      <c r="Y4" s="36">
-        <v>0</v>
-      </c>
-      <c r="Z4" s="37"/>
-      <c r="AA4" s="36">
-        <v>0</v>
-      </c>
-      <c r="AB4" s="37"/>
-      <c r="AC4" s="36">
-        <v>0</v>
-      </c>
-      <c r="AD4" s="37"/>
+      <c r="C4" s="27">
+        <v>0</v>
+      </c>
+      <c r="D4" s="28"/>
+      <c r="E4" s="27">
+        <v>0</v>
+      </c>
+      <c r="F4" s="28"/>
+      <c r="G4" s="27">
+        <v>0</v>
+      </c>
+      <c r="H4" s="28"/>
+      <c r="I4" s="27">
+        <v>0</v>
+      </c>
+      <c r="J4" s="28"/>
+      <c r="K4" s="27">
+        <v>0</v>
+      </c>
+      <c r="L4" s="28"/>
+      <c r="M4" s="27">
+        <v>0</v>
+      </c>
+      <c r="N4" s="28"/>
+      <c r="O4" s="27">
+        <v>0</v>
+      </c>
+      <c r="P4" s="28"/>
+      <c r="Q4" s="27">
+        <v>0</v>
+      </c>
+      <c r="R4" s="28"/>
+      <c r="S4" s="27">
+        <v>0</v>
+      </c>
+      <c r="T4" s="28"/>
+      <c r="U4" s="27">
+        <v>0</v>
+      </c>
+      <c r="V4" s="28"/>
+      <c r="W4" s="27">
+        <v>0</v>
+      </c>
+      <c r="X4" s="28"/>
+      <c r="Y4" s="27">
+        <v>0</v>
+      </c>
+      <c r="Z4" s="28"/>
+      <c r="AA4" s="27">
+        <v>0</v>
+      </c>
+      <c r="AB4" s="28"/>
+      <c r="AC4" s="27">
+        <v>0</v>
+      </c>
+      <c r="AD4" s="28"/>
     </row>
     <row r="5" spans="1:30" ht="30.75" x14ac:dyDescent="0.45">
       <c r="B5" s="10" t="s">
         <v>27</v>
       </c>
-      <c r="C5" s="36"/>
-      <c r="D5" s="37"/>
-      <c r="E5" s="36"/>
-      <c r="F5" s="37"/>
-      <c r="G5" s="36"/>
-      <c r="H5" s="37"/>
-      <c r="I5" s="36"/>
-      <c r="J5" s="37"/>
-      <c r="K5" s="36"/>
-      <c r="L5" s="37"/>
-      <c r="M5" s="36"/>
-      <c r="N5" s="37"/>
-      <c r="O5" s="36"/>
-      <c r="P5" s="37"/>
-      <c r="Q5" s="36"/>
-      <c r="R5" s="37"/>
-      <c r="S5" s="36"/>
-      <c r="T5" s="37"/>
-      <c r="U5" s="36"/>
-      <c r="V5" s="37"/>
-      <c r="W5" s="36"/>
-      <c r="X5" s="37"/>
-      <c r="Y5" s="36"/>
-      <c r="Z5" s="37"/>
-      <c r="AA5" s="36"/>
-      <c r="AB5" s="37"/>
-      <c r="AC5" s="36"/>
-      <c r="AD5" s="37"/>
+      <c r="C5" s="27"/>
+      <c r="D5" s="28"/>
+      <c r="E5" s="27"/>
+      <c r="F5" s="28"/>
+      <c r="G5" s="27"/>
+      <c r="H5" s="28"/>
+      <c r="I5" s="27"/>
+      <c r="J5" s="28"/>
+      <c r="K5" s="27"/>
+      <c r="L5" s="28"/>
+      <c r="M5" s="27"/>
+      <c r="N5" s="28"/>
+      <c r="O5" s="27"/>
+      <c r="P5" s="28"/>
+      <c r="Q5" s="27"/>
+      <c r="R5" s="28"/>
+      <c r="S5" s="27"/>
+      <c r="T5" s="28"/>
+      <c r="U5" s="27"/>
+      <c r="V5" s="28"/>
+      <c r="W5" s="27"/>
+      <c r="X5" s="28"/>
+      <c r="Y5" s="27"/>
+      <c r="Z5" s="28"/>
+      <c r="AA5" s="27"/>
+      <c r="AB5" s="28"/>
+      <c r="AC5" s="27"/>
+      <c r="AD5" s="28"/>
     </row>
     <row r="6" spans="1:30" ht="30.75" x14ac:dyDescent="0.45">
       <c r="B6" s="10" t="s">
         <v>28</v>
       </c>
-      <c r="C6" s="36"/>
-      <c r="D6" s="37"/>
-      <c r="E6" s="36"/>
-      <c r="F6" s="37"/>
-      <c r="G6" s="36"/>
-      <c r="H6" s="37"/>
-      <c r="I6" s="36"/>
-      <c r="J6" s="37"/>
-      <c r="K6" s="36"/>
-      <c r="L6" s="37"/>
-      <c r="M6" s="36"/>
-      <c r="N6" s="37"/>
-      <c r="O6" s="36"/>
-      <c r="P6" s="37"/>
-      <c r="Q6" s="36"/>
-      <c r="R6" s="37"/>
-      <c r="S6" s="36"/>
-      <c r="T6" s="37"/>
-      <c r="U6" s="36"/>
-      <c r="V6" s="37"/>
-      <c r="W6" s="36"/>
-      <c r="X6" s="37"/>
-      <c r="Y6" s="36"/>
-      <c r="Z6" s="37"/>
-      <c r="AA6" s="36"/>
-      <c r="AB6" s="37"/>
-      <c r="AC6" s="36"/>
-      <c r="AD6" s="37"/>
+      <c r="C6" s="27"/>
+      <c r="D6" s="28"/>
+      <c r="E6" s="27"/>
+      <c r="F6" s="28"/>
+      <c r="G6" s="27"/>
+      <c r="H6" s="28"/>
+      <c r="I6" s="27"/>
+      <c r="J6" s="28"/>
+      <c r="K6" s="27"/>
+      <c r="L6" s="28"/>
+      <c r="M6" s="27"/>
+      <c r="N6" s="28"/>
+      <c r="O6" s="27"/>
+      <c r="P6" s="28"/>
+      <c r="Q6" s="27"/>
+      <c r="R6" s="28"/>
+      <c r="S6" s="27"/>
+      <c r="T6" s="28"/>
+      <c r="U6" s="27"/>
+      <c r="V6" s="28"/>
+      <c r="W6" s="27"/>
+      <c r="X6" s="28"/>
+      <c r="Y6" s="27"/>
+      <c r="Z6" s="28"/>
+      <c r="AA6" s="27"/>
+      <c r="AB6" s="28"/>
+      <c r="AC6" s="27"/>
+      <c r="AD6" s="28"/>
     </row>
     <row r="7" spans="1:30" ht="46.15" x14ac:dyDescent="0.45">
       <c r="B7" s="10" t="s">
         <v>25</v>
       </c>
-      <c r="C7" s="36"/>
-      <c r="D7" s="37"/>
-      <c r="E7" s="36"/>
-      <c r="F7" s="37"/>
-      <c r="G7" s="36"/>
-      <c r="H7" s="37"/>
-      <c r="I7" s="36"/>
-      <c r="J7" s="37"/>
-      <c r="K7" s="36"/>
-      <c r="L7" s="37"/>
-      <c r="M7" s="36"/>
-      <c r="N7" s="37"/>
-      <c r="O7" s="36"/>
-      <c r="P7" s="37"/>
-      <c r="Q7" s="36"/>
-      <c r="R7" s="37"/>
-      <c r="S7" s="36"/>
-      <c r="T7" s="37"/>
-      <c r="U7" s="36"/>
-      <c r="V7" s="37"/>
-      <c r="W7" s="36"/>
-      <c r="X7" s="37"/>
-      <c r="Y7" s="36"/>
-      <c r="Z7" s="37"/>
-      <c r="AA7" s="36"/>
-      <c r="AB7" s="37"/>
-      <c r="AC7" s="36"/>
-      <c r="AD7" s="37"/>
+      <c r="C7" s="27"/>
+      <c r="D7" s="28"/>
+      <c r="E7" s="27"/>
+      <c r="F7" s="28"/>
+      <c r="G7" s="27"/>
+      <c r="H7" s="28"/>
+      <c r="I7" s="27"/>
+      <c r="J7" s="28"/>
+      <c r="K7" s="27"/>
+      <c r="L7" s="28"/>
+      <c r="M7" s="27"/>
+      <c r="N7" s="28"/>
+      <c r="O7" s="27"/>
+      <c r="P7" s="28"/>
+      <c r="Q7" s="27"/>
+      <c r="R7" s="28"/>
+      <c r="S7" s="27"/>
+      <c r="T7" s="28"/>
+      <c r="U7" s="27"/>
+      <c r="V7" s="28"/>
+      <c r="W7" s="27"/>
+      <c r="X7" s="28"/>
+      <c r="Y7" s="27"/>
+      <c r="Z7" s="28"/>
+      <c r="AA7" s="27"/>
+      <c r="AB7" s="28"/>
+      <c r="AC7" s="27"/>
+      <c r="AD7" s="28"/>
     </row>
     <row r="8" spans="1:30" ht="92.25" x14ac:dyDescent="0.45">
       <c r="B8" s="10" t="s">
         <v>29</v>
       </c>
-      <c r="C8" s="36"/>
-      <c r="D8" s="37"/>
-      <c r="E8" s="36"/>
-      <c r="F8" s="37"/>
-      <c r="G8" s="36"/>
-      <c r="H8" s="37"/>
-      <c r="I8" s="36"/>
-      <c r="J8" s="37"/>
-      <c r="K8" s="36"/>
-      <c r="L8" s="37"/>
-      <c r="M8" s="36"/>
-      <c r="N8" s="37"/>
-      <c r="O8" s="36"/>
-      <c r="P8" s="37"/>
-      <c r="Q8" s="36"/>
-      <c r="R8" s="37"/>
-      <c r="S8" s="36"/>
-      <c r="T8" s="37"/>
-      <c r="U8" s="36"/>
-      <c r="V8" s="37"/>
-      <c r="W8" s="36"/>
-      <c r="X8" s="37"/>
-      <c r="Y8" s="36"/>
-      <c r="Z8" s="37"/>
-      <c r="AA8" s="36"/>
-      <c r="AB8" s="37"/>
-      <c r="AC8" s="36"/>
-      <c r="AD8" s="37"/>
+      <c r="C8" s="27"/>
+      <c r="D8" s="28"/>
+      <c r="E8" s="27"/>
+      <c r="F8" s="28"/>
+      <c r="G8" s="27"/>
+      <c r="H8" s="28"/>
+      <c r="I8" s="27"/>
+      <c r="J8" s="28"/>
+      <c r="K8" s="27"/>
+      <c r="L8" s="28"/>
+      <c r="M8" s="27"/>
+      <c r="N8" s="28"/>
+      <c r="O8" s="27"/>
+      <c r="P8" s="28"/>
+      <c r="Q8" s="27"/>
+      <c r="R8" s="28"/>
+      <c r="S8" s="27"/>
+      <c r="T8" s="28"/>
+      <c r="U8" s="27"/>
+      <c r="V8" s="28"/>
+      <c r="W8" s="27"/>
+      <c r="X8" s="28"/>
+      <c r="Y8" s="27"/>
+      <c r="Z8" s="28"/>
+      <c r="AA8" s="27"/>
+      <c r="AB8" s="28"/>
+      <c r="AC8" s="27"/>
+      <c r="AD8" s="28"/>
     </row>
     <row r="9" spans="1:30" x14ac:dyDescent="0.45">
-      <c r="B9" s="10"/>
-      <c r="C9" s="36"/>
-      <c r="D9" s="37"/>
-      <c r="E9" s="36"/>
-      <c r="F9" s="37"/>
-      <c r="G9" s="36"/>
-      <c r="H9" s="37"/>
-      <c r="I9" s="36"/>
-      <c r="J9" s="37"/>
-      <c r="K9" s="36"/>
-      <c r="L9" s="37"/>
-      <c r="M9" s="36"/>
-      <c r="N9" s="37"/>
-      <c r="O9" s="36"/>
-      <c r="P9" s="37"/>
-      <c r="Q9" s="36"/>
-      <c r="R9" s="37"/>
-      <c r="S9" s="36"/>
-      <c r="T9" s="37"/>
-      <c r="U9" s="36"/>
-      <c r="V9" s="37"/>
-      <c r="W9" s="36"/>
-      <c r="X9" s="37"/>
-      <c r="Y9" s="36"/>
-      <c r="Z9" s="37"/>
-      <c r="AA9" s="36"/>
-      <c r="AB9" s="37"/>
-      <c r="AC9" s="36"/>
-      <c r="AD9" s="37"/>
+      <c r="B9" s="36"/>
+      <c r="C9" s="37"/>
+      <c r="D9" s="38"/>
+      <c r="E9" s="37"/>
+      <c r="F9" s="38"/>
+      <c r="G9" s="37"/>
+      <c r="H9" s="38"/>
+      <c r="I9" s="37"/>
+      <c r="J9" s="38"/>
+      <c r="K9" s="37"/>
+      <c r="L9" s="38"/>
+      <c r="M9" s="37"/>
+      <c r="N9" s="38"/>
+      <c r="O9" s="37"/>
+      <c r="P9" s="38"/>
+      <c r="Q9" s="37"/>
+      <c r="R9" s="38"/>
+      <c r="S9" s="37"/>
+      <c r="T9" s="38"/>
+      <c r="U9" s="37"/>
+      <c r="V9" s="38"/>
+      <c r="W9" s="37"/>
+      <c r="X9" s="38"/>
+      <c r="Y9" s="37"/>
+      <c r="Z9" s="38"/>
+      <c r="AA9" s="37"/>
+      <c r="AB9" s="38"/>
+      <c r="AC9" s="37"/>
+      <c r="AD9" s="38"/>
     </row>
     <row r="10" spans="1:30" s="2" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A10" s="1"/>
-      <c r="B10" s="11" t="s">
+      <c r="B10" s="39" t="s">
         <v>1</v>
       </c>
-      <c r="C10" s="26">
+      <c r="C10" s="40">
         <f>AVERAGE(C4:C9)</f>
         <v>0</v>
       </c>
-      <c r="D10" s="27"/>
-      <c r="E10" s="26">
+      <c r="D10" s="41"/>
+      <c r="E10" s="40">
         <f>AVERAGE(E4:E9)</f>
         <v>0</v>
       </c>
-      <c r="F10" s="27"/>
-      <c r="G10" s="26">
+      <c r="F10" s="41"/>
+      <c r="G10" s="40">
         <f>AVERAGE(G4:G9)</f>
         <v>0</v>
       </c>
-      <c r="H10" s="27"/>
-      <c r="I10" s="26">
+      <c r="H10" s="41"/>
+      <c r="I10" s="40">
         <f>AVERAGE(I4:I9)</f>
         <v>0</v>
       </c>
-      <c r="J10" s="27"/>
-      <c r="K10" s="26">
+      <c r="J10" s="41"/>
+      <c r="K10" s="40">
         <f>AVERAGE(K4:K9)</f>
         <v>0</v>
       </c>
-      <c r="L10" s="27"/>
-      <c r="M10" s="26">
+      <c r="L10" s="41"/>
+      <c r="M10" s="40">
         <f>AVERAGE(M4:M9)</f>
         <v>0</v>
       </c>
-      <c r="N10" s="27"/>
-      <c r="O10" s="26">
+      <c r="N10" s="41"/>
+      <c r="O10" s="40">
         <f>AVERAGE(O4:O9)</f>
         <v>0</v>
       </c>
-      <c r="P10" s="27"/>
-      <c r="Q10" s="26">
+      <c r="P10" s="41"/>
+      <c r="Q10" s="40">
         <f>AVERAGE(Q4:Q9)</f>
         <v>0</v>
       </c>
-      <c r="R10" s="27"/>
-      <c r="S10" s="26">
+      <c r="R10" s="41"/>
+      <c r="S10" s="40">
         <f>AVERAGE(S4:S9)</f>
         <v>0</v>
       </c>
-      <c r="T10" s="27"/>
-      <c r="U10" s="26">
+      <c r="T10" s="41"/>
+      <c r="U10" s="40">
         <f>AVERAGE(U4:U9)</f>
         <v>0</v>
       </c>
-      <c r="V10" s="27"/>
-      <c r="W10" s="26">
+      <c r="V10" s="41"/>
+      <c r="W10" s="40">
         <f>AVERAGE(W4:W9)</f>
         <v>0</v>
       </c>
-      <c r="X10" s="27"/>
-      <c r="Y10" s="26">
+      <c r="X10" s="41"/>
+      <c r="Y10" s="40">
         <f>AVERAGE(Y4:Y9)</f>
         <v>0</v>
       </c>
-      <c r="Z10" s="27"/>
-      <c r="AA10" s="26">
+      <c r="Z10" s="41"/>
+      <c r="AA10" s="40">
         <f>AVERAGE(AA4:AA9)</f>
         <v>0</v>
       </c>
-      <c r="AB10" s="27"/>
-      <c r="AC10" s="26">
+      <c r="AB10" s="41"/>
+      <c r="AC10" s="40">
         <f>AVERAGE(AC4:AC9)</f>
         <v>0</v>
       </c>
-      <c r="AD10" s="27"/>
+      <c r="AD10" s="41"/>
     </row>
     <row r="11" spans="1:30" s="7" customFormat="1" x14ac:dyDescent="0.45">
-      <c r="B11" s="17"/>
+      <c r="B11" s="16"/>
       <c r="C11" s="5"/>
       <c r="D11" s="5"/>
       <c r="E11" s="5"/>
